--- a/outputs/1925.xlsx
+++ b/outputs/1925.xlsx
@@ -183,11 +183,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -399,7 +399,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B6,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B6,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>NEW</v>
       </c>
     </row>
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B7,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B7,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>NEW</v>
       </c>
     </row>
@@ -417,7 +417,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B8,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B8,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>C</v>
       </c>
     </row>
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B9,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B9,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>D</v>
       </c>
     </row>
@@ -435,7 +435,7 @@
         <v>5</v>
       </c>
       <c r="C10" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B10,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B10,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>E</v>
       </c>
     </row>
@@ -444,7 +444,7 @@
         <v>6</v>
       </c>
       <c r="C11" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B11,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B11,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>F</v>
       </c>
     </row>
@@ -453,7 +453,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B12,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B12,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>G</v>
       </c>
     </row>
@@ -462,7 +462,7 @@
         <v>8</v>
       </c>
       <c r="C13" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B13,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B13,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>H</v>
       </c>
     </row>
@@ -471,7 +471,7 @@
         <v>9</v>
       </c>
       <c r="C14" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B14,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B14,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>NEW</v>
       </c>
     </row>
@@ -480,7 +480,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B15,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B15,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>J</v>
       </c>
     </row>
@@ -489,7 +489,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B16,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B16,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>K</v>
       </c>
     </row>
@@ -498,7 +498,7 @@
         <v>12</v>
       </c>
       <c r="C17" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B17,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B17,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>L</v>
       </c>
     </row>
@@ -507,7 +507,7 @@
         <v>13</v>
       </c>
       <c r="C18" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B18,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B18,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>M</v>
       </c>
     </row>
@@ -516,7 +516,7 @@
         <v>14</v>
       </c>
       <c r="C19" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B19,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B19,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>N</v>
       </c>
     </row>
@@ -525,7 +525,7 @@
         <v>15</v>
       </c>
       <c r="C20" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B20,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B20,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>O</v>
       </c>
     </row>
@@ -534,7 +534,7 @@
         <v>16</v>
       </c>
       <c r="C21" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B21,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B21,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>P</v>
       </c>
     </row>
@@ -543,7 +543,7 @@
         <v>17</v>
       </c>
       <c r="C22" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B22,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B22,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>Q</v>
       </c>
     </row>
@@ -552,7 +552,7 @@
         <v>18</v>
       </c>
       <c r="C23" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B23,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B23,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>R</v>
       </c>
     </row>
@@ -561,7 +561,7 @@
         <v>19</v>
       </c>
       <c r="C24" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B24,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B24,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>NEW</v>
       </c>
     </row>
@@ -570,7 +570,7 @@
         <v>20</v>
       </c>
       <c r="C25" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B25,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B25,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>NEW</v>
       </c>
     </row>
@@ -579,7 +579,7 @@
         <v>21</v>
       </c>
       <c r="C26" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B26,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B26,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>NEW</v>
       </c>
     </row>
@@ -588,7 +588,7 @@
         <v>22</v>
       </c>
       <c r="C27" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B27,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B27,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>NEW</v>
       </c>
     </row>
@@ -597,7 +597,7 @@
         <v>23</v>
       </c>
       <c r="C28" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B28,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B28,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>NEW</v>
       </c>
     </row>
@@ -606,7 +606,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B29,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B29,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>NEW</v>
       </c>
     </row>
@@ -615,7 +615,7 @@
         <v>25</v>
       </c>
       <c r="C30" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B30,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B30,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>NEW</v>
       </c>
     </row>
@@ -624,7 +624,7 @@
         <v>26</v>
       </c>
       <c r="C31" s="1" t="str">
-        <f aca="true">IFERROR(INDEX(OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),MATCH(Sheet1!B31,OFFSET(Sheet2!$A$5,0,MATCH(Sheet1!C$5,Sheet2!$A$5:$M$5,0)-1,18,1),0)),"NEW")</f>
+        <f aca="false">_xlfn.IFNA(INDEX(Sheet2!$A$6:$M$23,MATCH(Sheet1!B31,INDEX(Sheet2!$A$6:$M$23,0,MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),0),MATCH(Sheet1!$C$5,Sheet2!$A$5:$M$5,0)),"NEW")</f>
         <v>NEW</v>
       </c>
     </row>
